--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484349_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484349_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5649</v>
+        <v>1.5378</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3168</v>
+        <v>0.9434</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2481</v>
+        <v>0.5944</v>
       </c>
       <c r="G2" t="n">
         <v>-2.2636</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5753</v>
+        <v>1.5482</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1377</v>
+        <v>0.7644</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4375</v>
+        <v>0.7839</v>
       </c>
       <c r="V2" t="n">
         <v>4.5973</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0175</v>
+        <v>1.0336</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4512</v>
+        <v>1.1677</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4337</v>
+        <v>-0.1341</v>
       </c>
       <c r="G3" t="n">
         <v>-0.972</v>
@@ -688,13 +688,13 @@
         <v>0.7814</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7941</v>
+        <v>0.8103</v>
       </c>
       <c r="T3" t="n">
-        <v>0.831</v>
+        <v>0.5476</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0369</v>
+        <v>0.2626</v>
       </c>
       <c r="V3" t="n">
         <v>0.6093</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9404</v>
+        <v>0.3337</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5555</v>
+        <v>0.9488</v>
       </c>
       <c r="F4" t="n">
         <v>-0.615</v>
@@ -766,10 +766,10 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>1.051</v>
+        <v>0.4443</v>
       </c>
       <c r="T4" t="n">
-        <v>1.329</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="U4" t="n">
         <v>-0.278</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1864</v>
+        <v>-0.2348</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1979</v>
+        <v>0.2584</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3843</v>
+        <v>-0.4932</v>
       </c>
       <c r="G5" t="n">
         <v>1.9453</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6812</v>
+        <v>0.6328</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1845</v>
+        <v>0.245</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4967</v>
+        <v>0.3878</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6642</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6987</v>
+        <v>-0.8343</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7982</v>
+        <v>0.7171</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4969</v>
+        <v>-1.5514</v>
       </c>
       <c r="G6" t="n">
         <v>0.5626</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0009</v>
+        <v>0.8653</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9796</v>
+        <v>0.8985</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0213</v>
+        <v>-0.0332</v>
       </c>
       <c r="V6" t="n">
         <v>0.2772</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1616</v>
+        <v>-1.0504</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2525</v>
+        <v>-0.4953</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9091</v>
+        <v>-0.555</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7829</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6213</v>
+        <v>0.7325</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1337</v>
+        <v>0.8908</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5124</v>
+        <v>-0.1583</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3107</v>
+        <v>-1.9297</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.751</v>
+        <v>0.3891</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5597</v>
+        <v>-2.3188</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9372</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1686</v>
+        <v>-0.7958</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7687</v>
+        <v>-0.0665</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5927</v>
+        <v>1.2502</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0409</v>
+        <v>0.1023</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.1478</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3445</v>
+        <v>-2.1125</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2095</v>
+        <v>-0.8982</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.135</v>
+        <v>-1.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3967</v>
+        <v>-0.044</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>0.1156</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2152</v>
+        <v>-0.1597</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3402</v>
+        <v>-2.229</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0759</v>
+        <v>-1.751</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2643</v>
+        <v>-0.478</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.9372</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7958</v>
+        <v>-0.1686</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0665</v>
+        <v>-0.7687</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2502</v>
+        <v>-0.5927</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1023</v>
+        <v>0.0409</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1478</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1125</v>
+        <v>-0.3445</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8982</v>
+        <v>-0.2095</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2144</v>
+        <v>-0.135</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4545</v>
+        <v>-0.315</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3494</v>
+        <v>-0.1816</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1052</v>
+        <v>-0.1335</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.133</v>
+        <v>-3.3296</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2595</v>
+        <v>-1.5923</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8734</v>
+        <v>-1.7373</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0166</v>
@@ -1234,13 +1234,13 @@
         <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0578</v>
+        <v>0.7456</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0054</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0524</v>
+        <v>0.0838</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4959</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3078</v>
+        <v>-6.7027</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01930000000000032</v>
+        <v>0.5858999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.2883</v>
+        <v>-7.2884</v>
       </c>
       <c r="G11" t="n">
         <v>-7.139899999999999</v>
@@ -1312,13 +1312,13 @@
         <v>8.7904</v>
       </c>
       <c r="S11" t="n">
-        <v>4.814799999999999</v>
+        <v>5.42</v>
       </c>
       <c r="T11" t="n">
-        <v>4.059099999999999</v>
+        <v>4.664400000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7554</v>
+        <v>0.7553999999999998</v>
       </c>
       <c r="V11" t="n">
         <v>5.761</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7779</v>
+        <v>4.5286</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2014</v>
+        <v>3.3025</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5765</v>
+        <v>1.2261</v>
       </c>
       <c r="G12" t="n">
         <v>3.2492</v>
@@ -1390,13 +1390,13 @@
         <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5066</v>
+        <v>-0.7559</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5501</v>
+        <v>-0.449</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9565</v>
+        <v>-0.3069</v>
       </c>
       <c r="V12" t="n">
         <v>0.2772</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6437</v>
+        <v>4.4475</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2797</v>
+        <v>5.3808</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6361</v>
+        <v>-0.9334</v>
       </c>
       <c r="G13" t="n">
         <v>1.8096</v>
@@ -1468,13 +1468,13 @@
         <v>2.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.0969</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0497</v>
+        <v>0.1508</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9504</v>
+        <v>-0.2477</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.008</v>
+        <v>1.4476</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5744</v>
+        <v>-0.6755</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5825</v>
+        <v>2.1231</v>
       </c>
       <c r="G14" t="n">
         <v>0.3504</v>
@@ -1546,13 +1546,13 @@
         <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3191</v>
+        <v>0.1204</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0384</v>
+        <v>-0.1395</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2807</v>
+        <v>0.2599</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8504</v>
+        <v>0.5658</v>
       </c>
       <c r="E15" t="n">
-        <v>3.449</v>
+        <v>-1.0026</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5985</v>
+        <v>1.5684</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7238</v>
+        <v>0.0114</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2676</v>
+        <v>-0.5682</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4562</v>
+        <v>0.5795</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4829</v>
+        <v>-0.5927</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0261</v>
+        <v>-0.6332</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4568</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7591</v>
+        <v>0.6041</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7585</v>
+        <v>0.065</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.5391</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3333</v>
+        <v>-0.227</v>
       </c>
       <c r="T15" t="n">
-        <v>2.779</v>
+        <v>-0.4099</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4458</v>
+        <v>0.1829</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.5973</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.9331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3751</v>
+        <v>0.4722</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0026</v>
+        <v>-0.191</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3777</v>
+        <v>0.6632</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0114</v>
+        <v>0.1388</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5682</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5795</v>
+        <v>-0.6883</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5927</v>
+        <v>1.1076</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6332</v>
+        <v>1.6603</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>-0.5527</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6041</v>
+        <v>-0.9688</v>
       </c>
       <c r="N16" t="n">
-        <v>0.065</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5391</v>
+        <v>-0.1356</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4176</v>
+        <v>-0.3893</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4099</v>
+        <v>-0.3218</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0077</v>
+        <v>-0.0675</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2039</v>
+        <v>0.4491</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.191</v>
+        <v>1.7805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3949</v>
+        <v>-1.3315</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1388</v>
+        <v>0.3044</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.1957</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6883</v>
+        <v>-0.8912</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1076</v>
+        <v>2.502</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6603</v>
+        <v>2.8524</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5527</v>
+        <v>-0.3504</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9688</v>
+        <v>-2.1975</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.6567</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1356</v>
+        <v>-0.5409</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>3.1255</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6576</v>
+        <v>-0.3129</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3218</v>
+        <v>-0.1587</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3358</v>
+        <v>-0.1542</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3321</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6121</v>
+        <v>0.1839</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2825</v>
+        <v>-0.6758</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6704</v>
+        <v>0.8597</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2269</v>
@@ -1858,13 +1858,13 @@
         <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0614</v>
+        <v>-0.2655</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4842</v>
+        <v>0.1225</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5773</v>
+        <v>-0.388</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2772</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7694</v>
+        <v>-0.7</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0727</v>
+        <v>1.6289</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8422</v>
+        <v>-2.3289</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3044</v>
+        <v>2.7238</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1957</v>
+        <v>1.2676</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8912</v>
+        <v>1.4562</v>
       </c>
       <c r="J19" t="n">
-        <v>2.502</v>
+        <v>3.4829</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8524</v>
+        <v>2.0261</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3504</v>
+        <v>1.4568</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1975</v>
+        <v>-0.7591</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6567</v>
+        <v>-0.7585</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5409</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1255</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5314</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8665</v>
+        <v>0.959</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6649</v>
+        <v>-0.1761</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4959</v>
+        <v>-4.5973</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6093</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1052</v>
+        <v>-3.9331</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1698</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9412</v>
+        <v>-2.5367</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7714</v>
+        <v>1.8205</v>
       </c>
       <c r="G20" t="n">
         <v>-0.221</v>
@@ -2014,13 +2014,13 @@
         <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7534</v>
+        <v>-0.2999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9133</v>
+        <v>-0.5088</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1599</v>
+        <v>0.2089</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>7.307699999999999</v>
+        <v>10.6785</v>
       </c>
       <c r="E21" t="n">
         <v>7.011099999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2965999999999998</v>
+        <v>3.6672</v>
       </c>
       <c r="G21" t="n">
         <v>7.139699999999999</v>
@@ -2068,10 +2068,10 @@
         <v>15.7804</v>
       </c>
       <c r="K21" t="n">
-        <v>9.704500000000001</v>
+        <v>9.704499999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>6.075899999999999</v>
+        <v>6.0759</v>
       </c>
       <c r="M21" t="n">
         <v>-8.6404</v>
@@ -2092,13 +2092,13 @@
         <v>19.5343</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.8145</v>
+        <v>-1.4442</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7555000000000001</v>
+        <v>-0.7554000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.0592</v>
+        <v>-0.6887</v>
       </c>
       <c r="V21" t="n">
         <v>-5.7611</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484349_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484349_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5378</v>
+        <v>1.0336</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9434</v>
+        <v>1.1677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5944</v>
+        <v>-0.1341</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2636</v>
+        <v>-0.972</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6994</v>
+        <v>-1.1737</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.5641</v>
+        <v>0.2017</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3481</v>
+        <v>0.2061</v>
       </c>
       <c r="K2" t="n">
-        <v>0.967</v>
+        <v>0.0038</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6188</v>
+        <v>0.2023</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6117</v>
+        <v>-1.1781</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6664</v>
+        <v>-1.1775</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9453</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.1022</v>
+        <v>-0.1953</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5482</v>
+        <v>0.8103</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7644</v>
+        <v>0.5476</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7839</v>
+        <v>0.2626</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5973</v>
+        <v>0.6093</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9331</v>
+        <v>0.6093</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0336</v>
+        <v>0.914</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1677</v>
+        <v>0.914</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1341</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.972</v>
+        <v>0.914</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1737</v>
+        <v>0.307</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2017</v>
+        <v>0.607</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2061</v>
+        <v>0.914</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0038</v>
+        <v>0.307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2023</v>
+        <v>0.607</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1781</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1775</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8103</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5476</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2626</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3337</v>
+        <v>0.6239</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9488</v>
+        <v>0.0295</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.615</v>
+        <v>0.5944</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.8131</v>
+        <v>-3.1775</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7199</v>
+        <v>-1.0064</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0932</v>
+        <v>-2.1711</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1649</v>
+        <v>-0.5658</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0435</v>
+        <v>0.66</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1214</v>
+        <v>-1.2258</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9779</v>
+        <v>-2.6117</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7634</v>
+        <v>-1.6664</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2146</v>
+        <v>-0.9453</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9534</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9301</v>
+        <v>-4.1022</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4443</v>
+        <v>1.5482</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7644</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.278</v>
+        <v>0.7839</v>
       </c>
       <c r="V4" t="n">
-        <v>3.6559</v>
+        <v>4.5973</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9917</v>
+        <v>3.9331</v>
       </c>
       <c r="X4" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2348</v>
+        <v>0.3337</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2584</v>
+        <v>0.9488</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4932</v>
+        <v>-0.615</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9453</v>
+        <v>-1.8131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2456</v>
+        <v>-0.7199</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6998</v>
+        <v>-1.0932</v>
       </c>
       <c r="J5" t="n">
-        <v>3.803</v>
+        <v>0.1649</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2931</v>
+        <v>0.0435</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5099</v>
+        <v>0.1214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8577</v>
+        <v>-1.9779</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0476</v>
+        <v>-0.7634</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8101</v>
+        <v>-1.2146</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R5" t="n">
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6328</v>
+        <v>0.4443</v>
       </c>
       <c r="T5" t="n">
-        <v>0.245</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3878</v>
+        <v>-0.278</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6642</v>
+        <v>3.6559</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6642</v>
+        <v>2.9917</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8343</v>
+        <v>-0.2348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7171</v>
+        <v>0.2584</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5514</v>
+        <v>-0.4932</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5626</v>
+        <v>1.9453</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4088</v>
+        <v>0.2456</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8462</v>
+        <v>1.6998</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6436</v>
+        <v>3.803</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5447</v>
+        <v>1.2931</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.9011</v>
+        <v>2.5099</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.081</v>
+        <v>-1.8577</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1358</v>
+        <v>-1.0476</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.8101</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5395</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1022</v>
+        <v>-3.1255</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8653</v>
+        <v>0.6328</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8985</v>
+        <v>0.245</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0332</v>
+        <v>0.3878</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0504</v>
+        <v>-0.8343</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4953</v>
+        <v>0.7171</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.555</v>
+        <v>-1.5514</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7829</v>
+        <v>0.5626</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2292</v>
+        <v>2.4088</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5537</v>
+        <v>-1.8462</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4094</v>
+        <v>3.6436</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5308</v>
+        <v>4.5447</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1214</v>
+        <v>-0.9011</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3735</v>
+        <v>-3.081</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6984</v>
+        <v>-2.1358</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6751</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7325</v>
+        <v>0.8653</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8908</v>
+        <v>0.8985</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1583</v>
+        <v>-0.0332</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9297</v>
+        <v>-1.0504</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3891</v>
+        <v>-0.4953</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3188</v>
+        <v>-0.555</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-1.7829</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7958</v>
+        <v>-1.2292</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0665</v>
+        <v>-0.5537</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2502</v>
+        <v>-0.4094</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1023</v>
+        <v>-0.5308</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1478</v>
+        <v>0.1214</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1125</v>
+        <v>-1.3735</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8982</v>
+        <v>-0.6984</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2144</v>
+        <v>-0.6751</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.044</v>
+        <v>0.7325</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1156</v>
+        <v>0.8908</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1597</v>
+        <v>-0.1583</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.229</v>
+        <v>-1.9297</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.751</v>
+        <v>0.3891</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.478</v>
+        <v>-2.3188</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9372</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1686</v>
+        <v>-0.7958</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7687</v>
+        <v>-0.0665</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5927</v>
+        <v>1.2502</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0409</v>
+        <v>0.1023</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.1478</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3445</v>
+        <v>-2.1125</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2095</v>
+        <v>-0.8982</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.135</v>
+        <v>-1.2144</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.315</v>
+        <v>-0.044</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1816</v>
+        <v>0.1156</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1335</v>
+        <v>-0.1597</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3296</v>
+        <v>-2.229</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5923</v>
+        <v>-1.751</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7373</v>
+        <v>-0.478</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0166</v>
+        <v>-0.9372</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3863</v>
+        <v>-0.1686</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4029</v>
+        <v>-0.7687</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2267</v>
+        <v>-0.5927</v>
       </c>
       <c r="K10" t="n">
-        <v>1.494</v>
+        <v>0.0409</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2673</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2433</v>
+        <v>-0.3445</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1077</v>
+        <v>-0.2095</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1356</v>
+        <v>-0.135</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5627</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7456</v>
+        <v>-0.315</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.1816</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0838</v>
+        <v>-0.1335</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,151 +1317,157 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7027</v>
+        <v>-3.3296</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5858999999999999</v>
+        <v>-1.5923</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.2884</v>
+        <v>-1.7373</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.139899999999999</v>
+        <v>-1.0166</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7459</v>
+        <v>0.3863</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.3938</v>
+        <v>-1.4029</v>
       </c>
       <c r="J11" t="n">
-        <v>8.640499999999999</v>
+        <v>0.2267</v>
       </c>
       <c r="K11" t="n">
-        <v>7.958499999999999</v>
+        <v>1.494</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6819999999999995</v>
+        <v>-1.2673</v>
       </c>
       <c r="M11" t="n">
-        <v>-15.7802</v>
+        <v>-1.2433</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.704499999999999</v>
+        <v>-1.1077</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.0758</v>
+        <v>-0.1356</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.7439</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-19.5342</v>
+        <v>-2.1488</v>
       </c>
       <c r="R11" t="n">
-        <v>8.7904</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>5.42</v>
+        <v>0.7456</v>
       </c>
       <c r="T11" t="n">
-        <v>4.664400000000001</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7553999999999998</v>
+        <v>0.0838</v>
       </c>
       <c r="V11" t="n">
-        <v>5.761</v>
+        <v>-1.4959</v>
       </c>
       <c r="W11" t="n">
-        <v>6.815</v>
+        <v>-0.3321</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.054</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5286</v>
+        <v>-6.702600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3025</v>
+        <v>0.5860000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2261</v>
+        <v>-7.2884</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2492</v>
+        <v>-7.139799999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5009</v>
+        <v>-1.7459</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7501</v>
+        <v>-5.3938</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4743</v>
+        <v>8.640599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.142</v>
+        <v>7.9585</v>
       </c>
       <c r="L12" t="n">
-        <v>3.6163</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2251</v>
+        <v>-15.7802</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3589</v>
+        <v>-9.704499999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1338</v>
+        <v>-6.0758</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7581</v>
+        <v>-10.7439</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-19.5342</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7581</v>
+        <v>8.7904</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7559</v>
+        <v>5.42</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.449</v>
+        <v>4.6644</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3069</v>
+        <v>0.7554</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>5.760999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>6.815</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.054</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1479,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4475</v>
+        <v>4.5286</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3808</v>
+        <v>3.3025</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9334</v>
+        <v>1.2261</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8096</v>
+        <v>3.2492</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7309</v>
+        <v>-0.5009</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0788</v>
+        <v>3.7501</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2068</v>
+        <v>3.4743</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3177</v>
+        <v>-0.142</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8891</v>
+        <v>3.6163</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3971</v>
+        <v>-0.2251</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5868</v>
+        <v>-0.3589</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8103</v>
+        <v>0.1338</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9301</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0969</v>
+        <v>-0.7559</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1508</v>
+        <v>-0.449</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2477</v>
+        <v>-0.3069</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4476</v>
+        <v>4.4475</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6755</v>
+        <v>5.3808</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1231</v>
+        <v>-0.9334</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3504</v>
+        <v>1.8096</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7282999999999999</v>
+        <v>0.7309</v>
       </c>
       <c r="I14" t="n">
         <v>1.0788</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1049</v>
+        <v>4.2068</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2443</v>
+        <v>2.3177</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3492</v>
+        <v>1.8891</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7544</v>
+        <v>-2.3971</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.484</v>
+        <v>-1.5868</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2704</v>
+        <v>-0.8103</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>2.7348</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1204</v>
+        <v>-0.0969</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1395</v>
+        <v>0.1508</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2599</v>
+        <v>-0.2477</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5658</v>
+        <v>1.4476</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0026</v>
+        <v>-0.6755</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5684</v>
+        <v>2.1231</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0114</v>
+        <v>0.3504</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5682</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5795</v>
+        <v>1.0788</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5927</v>
+        <v>1.1049</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6332</v>
+        <v>-0.2443</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>1.3492</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6041</v>
+        <v>-0.7544</v>
       </c>
       <c r="N15" t="n">
-        <v>0.065</v>
+        <v>-0.484</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5391</v>
+        <v>-0.2704</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.227</v>
+        <v>0.1204</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4099</v>
+        <v>-0.1395</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1829</v>
+        <v>0.2599</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4722</v>
+        <v>0.5658</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.191</v>
+        <v>-1.0026</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6632</v>
+        <v>1.5684</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1388</v>
+        <v>0.0114</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.5682</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6883</v>
+        <v>0.5795</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1076</v>
+        <v>-0.5927</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6603</v>
+        <v>-0.6332</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5527</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9688</v>
+        <v>0.6041</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1356</v>
+        <v>0.5391</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3893</v>
+        <v>-0.227</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3218</v>
+        <v>-0.4099</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0675</v>
+        <v>0.1829</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4491</v>
+        <v>0.4722</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7805</v>
+        <v>-0.191</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3315</v>
+        <v>0.6632</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3044</v>
+        <v>0.1388</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1957</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8912</v>
+        <v>-0.6883</v>
       </c>
       <c r="J17" t="n">
-        <v>2.502</v>
+        <v>1.1076</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8524</v>
+        <v>1.6603</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3504</v>
+        <v>-0.5527</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1975</v>
+        <v>-0.9688</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6567</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5409</v>
+        <v>-0.1356</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1255</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3129</v>
+        <v>-0.3893</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1587</v>
+        <v>-0.3218</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1542</v>
+        <v>-0.0675</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1052</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1839</v>
+        <v>0.4491</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6758</v>
+        <v>1.7805</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8597</v>
+        <v>-1.3315</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2269</v>
+        <v>0.3044</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3106</v>
+        <v>1.1957</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9163</v>
+        <v>-0.8912</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.603</v>
+        <v>2.502</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7176</v>
+        <v>2.8524</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3206</v>
+        <v>-0.3504</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6239</v>
+        <v>-2.1975</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0281</v>
+        <v>-1.6567</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4043</v>
+        <v>-0.5409</v>
       </c>
       <c r="P18" t="n">
         <v>1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>3.1255</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2655</v>
+        <v>-0.3129</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1225</v>
+        <v>-0.1587</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.388</v>
+        <v>-0.1542</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7</v>
+        <v>0.1839</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6289</v>
+        <v>-0.6758</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3289</v>
+        <v>0.8597</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7238</v>
+        <v>-1.2269</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2676</v>
+        <v>-0.3106</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4562</v>
+        <v>-0.9163</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4829</v>
+        <v>-0.603</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0261</v>
+        <v>0.7176</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4568</v>
+        <v>-1.3206</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7591</v>
+        <v>-0.6239</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7585</v>
+        <v>-1.0281</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4043</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7828000000000001</v>
+        <v>-0.2655</v>
       </c>
       <c r="T19" t="n">
-        <v>0.959</v>
+        <v>0.1225</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1761</v>
+        <v>-0.388</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.5973</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.9331</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5367</v>
+        <v>1.6289</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8205</v>
+        <v>-2.3289</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.221</v>
+        <v>2.7238</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1673</v>
+        <v>1.2676</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0537</v>
+        <v>1.4562</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0976</v>
+        <v>3.4829</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1499</v>
+        <v>2.0261</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0523</v>
+        <v>1.4568</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3186</v>
+        <v>-0.7591</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3172</v>
+        <v>-0.7585</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0014</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9301</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2999</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5088</v>
+        <v>0.959</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2089</v>
+        <v>-0.1761</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-4.5973</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.9331</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,152 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-0.7161999999999999</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.5367</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.8205</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.221</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.1673</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.0537</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.0976</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.1499</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.0523</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.3186</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.3172</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.2999</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.5088</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2089</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484349_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>10.6785</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>7.011099999999999</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>3.6672</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>7.139699999999999</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>1.746</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>5.393899999999999</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>15.7804</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>9.704499999999999</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>6.0759</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>-8.6404</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>-7.9584</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>-0.6820000000000001</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>10.7439</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>-8.7904</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>19.5343</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>-1.4442</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>-0.7554000000000001</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>-0.6887</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V22" t="n">
         <v>-5.7611</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W22" t="n">
         <v>0.7766999999999999</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X22" t="n">
         <v>-6.5378</v>
       </c>
+      <c r="Y22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
